--- a/تكنولوجيا ترم اول.xlsx
+++ b/تكنولوجيا ترم اول.xlsx
@@ -4378,13 +4378,13 @@
         <v>مستجد</v>
       </c>
       <c r="F20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>5</v>
       </c>
       <c r="H20">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I20">
         <v>15</v>
@@ -4393,7 +4393,7 @@
         <v>16</v>
       </c>
       <c r="K20">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
@@ -4553,22 +4553,22 @@
         <v>مستجد</v>
       </c>
       <c r="F25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>5</v>
       </c>
       <c r="H25">
+        <v>15</v>
+      </c>
+      <c r="I25">
         <v>13</v>
-      </c>
-      <c r="I25">
-        <v>12</v>
       </c>
       <c r="J25">
         <v>22</v>
       </c>
       <c r="K25">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
@@ -6757,22 +6757,22 @@
         <v>مستجد</v>
       </c>
       <c r="F25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>4</v>
       </c>
       <c r="H25">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J25">
         <v>24</v>
       </c>
       <c r="K25">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
@@ -7789,13 +7789,13 @@
         <v>باقي</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>6</v>
       </c>
       <c r="H23">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I23">
         <v>12</v>
@@ -7804,7 +7804,7 @@
         <v>22</v>
       </c>
       <c r="K23">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
